--- a/B-6/Assets/Resources/Json/player/player_data.xlsx
+++ b/B-6/Assets/Resources/Json/player/player_data.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="63" documentId="11_6E8EAB6661E618BD64B32149CAC7046F2BCFF665" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{825572CA-C4F3-4CE4-B5EE-2B19781FEF75}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\タワーディフェンスローグライク\学校\B-6\Assets\Resources\Json\player\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E65754-8CD8-47B2-825E-AA59086EC648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -58,11 +66,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -70,8 +78,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -420,9 +435,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -445,7 +460,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -465,10 +480,10 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -488,10 +503,10 @@
         <v>5</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -511,10 +526,10 @@
         <v>5</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -534,26 +549,16 @@
         <v>5</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45e75c57-a883-4f1a-8e28-effa0a633cfd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100CA2EEB5C486BA448AC1B54B2E38D6833" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="a0e8d859f13fcc4ef53aae1bf113f035">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="45e75c57-a883-4f1a-8e28-effa0a633cfd" xmlns:ns3="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="748b9a06c6582f68083b9ca7ee3bd5aa" ns2:_="" ns3:_="">
     <xsd:import namespace="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
@@ -748,6 +753,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45e75c57-a883-4f1a-8e28-effa0a633cfd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -758,13 +774,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C0A7E7A-B940-40D6-B4F2-FF40EF6B591F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B99D8D32-D122-4962-8C59-C50F7265F223}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
+    <ds:schemaRef ds:uri="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B99D8D32-D122-4962-8C59-C50F7265F223}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C0A7E7A-B940-40D6-B4F2-FF40EF6B591F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
+    <ds:schemaRef ds:uri="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97F9971E-2CB9-4355-B636-B2B93991C1DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97F9971E-2CB9-4355-B636-B2B93991C1DA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/B-6/Assets/Resources/Json/player/player_data.xlsx
+++ b/B-6/Assets/Resources/Json/player/player_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\タワーディフェンスローグライク\学校\B-6\Assets\Resources\Json\player\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E65754-8CD8-47B2-825E-AA59086EC648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24BDAA3-438A-42F6-A306-B6ECD52603C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -465,7 +465,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -474,7 +474,7 @@
         <v>1.2</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -488,7 +488,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -497,7 +497,7 @@
         <v>1.2</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -511,7 +511,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -520,7 +520,7 @@
         <v>1.2</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -534,7 +534,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -543,7 +543,7 @@
         <v>1.2</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -559,6 +559,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45e75c57-a883-4f1a-8e28-effa0a633cfd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100CA2EEB5C486BA448AC1B54B2E38D6833" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="a0e8d859f13fcc4ef53aae1bf113f035">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="45e75c57-a883-4f1a-8e28-effa0a633cfd" xmlns:ns3="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="748b9a06c6582f68083b9ca7ee3bd5aa" ns2:_="" ns3:_="">
     <xsd:import namespace="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
@@ -753,17 +764,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45e75c57-a883-4f1a-8e28-effa0a633cfd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -774,6 +774,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C0A7E7A-B940-40D6-B4F2-FF40EF6B591F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
+    <ds:schemaRef ds:uri="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B99D8D32-D122-4962-8C59-C50F7265F223}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -792,17 +803,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C0A7E7A-B940-40D6-B4F2-FF40EF6B591F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
-    <ds:schemaRef ds:uri="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97F9971E-2CB9-4355-B636-B2B93991C1DA}">
   <ds:schemaRefs>

--- a/B-6/Assets/Resources/Json/player/player_data.xlsx
+++ b/B-6/Assets/Resources/Json/player/player_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\タワーディフェンスローグライク\学校\B-6\Assets\Resources\Json\player\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6df029749d5c6239/デスクトップ/タワーディフェンス/B-6/Assets/Resources/Json/player/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24BDAA3-438A-42F6-A306-B6ECD52603C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{E24BDAA3-438A-42F6-A306-B6ECD52603C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6E70DA7-3A95-44C4-B9C4-B71F8C43F2B6}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,9 +30,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -435,9 +432,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -460,7 +457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -483,7 +480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -500,13 +497,13 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -523,13 +520,13 @@
         <v>20</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G4">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -559,17 +556,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45e75c57-a883-4f1a-8e28-effa0a633cfd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100CA2EEB5C486BA448AC1B54B2E38D6833" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="a0e8d859f13fcc4ef53aae1bf113f035">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="45e75c57-a883-4f1a-8e28-effa0a633cfd" xmlns:ns3="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="748b9a06c6582f68083b9ca7ee3bd5aa" ns2:_="" ns3:_="">
     <xsd:import namespace="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
@@ -764,6 +750,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45e75c57-a883-4f1a-8e28-effa0a633cfd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -774,17 +771,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C0A7E7A-B940-40D6-B4F2-FF40EF6B591F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
-    <ds:schemaRef ds:uri="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B99D8D32-D122-4962-8C59-C50F7265F223}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -803,6 +789,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C0A7E7A-B940-40D6-B4F2-FF40EF6B591F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="45e75c57-a883-4f1a-8e28-effa0a633cfd"/>
+    <ds:schemaRef ds:uri="d158fb7b-fca2-44d6-b599-d1df5b4c5c0d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97F9971E-2CB9-4355-B636-B2B93991C1DA}">
   <ds:schemaRefs>

--- a/B-6/Assets/Resources/Json/player/player_data.xlsx
+++ b/B-6/Assets/Resources/Json/player/player_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6df029749d5c6239/デスクトップ/タワーディフェンス/B-6/Assets/Resources/Json/player/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6df029749d5c6239/デスクトップ/1009/B-6/Assets/Resources/Json/player/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{E24BDAA3-438A-42F6-A306-B6ECD52603C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6E70DA7-3A95-44C4-B9C4-B71F8C43F2B6}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{E24BDAA3-438A-42F6-A306-B6ECD52603C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3AA0851-C89F-4C8B-87BE-AF121F898C97}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -142,6 +142,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -462,7 +466,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -471,7 +475,7 @@
         <v>1.2</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -485,7 +489,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -494,7 +498,7 @@
         <v>1.2</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F3">
         <v>9</v>
@@ -508,7 +512,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -517,7 +521,7 @@
         <v>1.2</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F4">
         <v>7</v>
@@ -531,7 +535,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -540,7 +544,7 @@
         <v>1.2</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>5</v>
